--- a/交接清單/skill架構內容.xlsx
+++ b/交接清單/skill架構內容.xlsx
@@ -7,12 +7,17 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="網站精神(原話原則)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="技術架構" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="已建置公司(50+)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="股票APP-台股版對照" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="需求追蹤清單" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="錯誤紀錄" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="網站精神(原話原則)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="技術架構" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="已建置公司(50+)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="股票APP-台股版對照" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'需求追蹤清單'!$A$1:$F$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'錯誤紀錄'!$A$1:$F$12</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,8 +42,13 @@
       <b val="1"/>
       <color rgb="00C00000"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -50,8 +60,23 @@
         <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -73,11 +98,25 @@
         <color rgb="00BBBBBB"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -87,6 +126,24 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -453,6 +510,1420 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="58" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>分類</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>需求內容（使用者提出）</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>狀態</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>完成方式／備註</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>長期</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>最高鐵則</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>一律免費，禁止任何付款；可能計費前必先詢問</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>資料源/AI/部署全免費；Vercel+Groq/OpenRouter 免費額度</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>長期</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>最高鐵則</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>所有回覆一律繁體中文，專有名詞中譯附英文縮寫</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>全站與所有回覆遵循</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>長期</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>最高鐵則</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>修正後要自我驗證，不可讓使用者測試才發現問題</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>⏳ 進行中</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>已改為每次改完在線上實機驗證；仍有漏網（見錯誤紀錄）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>長期</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>最高鐵則</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>手機 APP 畫面優先，一律用 390px 驗證</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>所有驗證改用 390x844；並加測 320px 極窄</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>長期</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>資料原則</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>法說會與產品一律官網 IR 優先，找不到才退回 SEC</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>IR_CALL_SUMMARY/IR_PRODUCTS_SUMMARY 人工判讀；2026-08-03 修正成長動能判斷也改 IR 優先</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>長期</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>資料原則</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>以事實為依據，絕不 AI 臆造數字</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>數字類只能引用真實數據/官方原文</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>長期</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>自動化</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>每季法說會後主動更新，不等使用者提醒</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>每次對話主動檢查待更新季度</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>長期</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>版面</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>版面已定案，不主動提議改版</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>已否決 5 種風格</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>長期</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>交接</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>上下文快滿時提醒並更新交接手冊</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>PreCompact hook + 交接記錄.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>台股估值卡要有本益比（同美股）</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>loadYahooFin 取 trailingPeRatio + computePe5yRange</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>台股要有 5 年本益比區間與視覺化 gauge</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>renderTwPeChecklist 量表</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>台股要有 7 項選股準則檢查清單</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>與美股同一套邏輯</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>台股要有版主選股判斷結論</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>tw_chk_verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>管理</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>所有需求列入 CLAUDE.md 並標示完成狀態</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>交接清單/CLAUDE.md 附錄 B</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>管理</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>開新 session 時確認有無遺漏未完成事項</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>CLAUDE.md 第 10 節四步驟</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>上架</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Google Play 上架</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>⏸️ 暫緩</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>使用者決定：等 app 完美時自己提出，勿主動推進</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>修正</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>美股台積電與台股台積電內容不同（投資總結／估值）</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>台股誤用進行中年度→改用最後完整年度；ROE 9.7%→31.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>修正</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>諾和諾德盤前股價正確但漲跌幅錯誤</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>基準改用 regularMarketPrice，移除會差一天的 chartPreviousClose</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>修正</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>打開 App 點選單顯示建置中，要先點 AI 鈕才有內容</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>移除過時文字＋autoLoadDefaultStock 自動載入</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>修正</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>手機看台股產品與服務等選單沒內容</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>同上；並確認 21 檔台股 IR 內容零缺漏</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>版面</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>財經新聞移到自選股後、法說會未來前景接其後</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>#grpMenu 按鈕順序調整</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>管理</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>在 skill架構內容.xlsx 新增清單追蹤需求／錯誤／待辦</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>本表 + 錯誤紀錄表</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>管理</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>後續新需求都要列入本檔，每天開始前先確認清單</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>⏳ 進行中</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>已寫入 CLAUDE.md 開場流程，每次對話先讀本檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>排程</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>季度更新</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>研華(2395) Q2 法說會 8/5</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>📅 排程中</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>待法說會後更新 IR 常數</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>排程</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>季度更新</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>廣達(2382) Q2 正式版 8/12</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>📅 排程中</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>目前僅月營收，待補 EPS/毛利率/展望</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>排程</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>季度更新</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>和碩(4938) Q2 法說會 8/12</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>📅 排程中</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>排程</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>季度更新</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>群聯(8299) Q2 法說會 8/13</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>📅 排程中</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>排程</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>季度更新</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>華碩2357/聯詠3034/中華電2412/仁寶2324 Q2</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>📅 排程中</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>法說會日期待公告</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>排程</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>季度更新</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>美股 SPOT Q2(8/4)、NVO H1(~8/5-6)、SMCI(8/11)</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>📅 排程中</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>排程</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>季度更新</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>美股 8 月中下旬密集：AMD/PLTR/UBER/ABNB/MCD/DIS</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>📅 排程中</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>版面</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>AI技術分析移到法說會後，護城河與彼得林區分類緊接其後</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>#grpMenu 按鈕順序調整</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>版面</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>台股載入進度和美股一樣移到大盤指數選單</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>logPanel 移到 indexBar 後，syncLogPanel() 依選單顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>自選股的編輯拖曳功能很難用</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>改用 ▲▼ 上下移按鈕；moveWatchlistItem 原本是沒接 UI 的死程式碼</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F34"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>使用者回報的問題</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>真正原因</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>狀態</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>修正方式／學到的教訓</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>美股台積電與台股台積電的投資總結／估值內容不同</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>台股把進行中的 2026 年度（僅到 Q1/Q2）當完整年度做選股準則：半年淨利÷全年股東權益 → ROE 只剩 9.7%（實際 31.7%）。美股用最後完整年度 2025。</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>進行中年度不算 ROE（留白）；準則一律取最後完整年度。教訓：同一指標在兩個市場要用同一個「期間定義」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>台積電美股與台股引用的資本支出數字不同</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>美股用 SEC 自動擷取的舊指引（520~560億），蓋過人工判讀的官網 IR 最新值（600~640億，2026/07/16 已上修），違反「官網 IR 優先」原則。</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>callGemini 集中改為 IR 優先；並加來源優先序鐵則。教訓：顯示邏輯已是 IR 優先，送 AI 判斷的依據也必須一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>台積電台股「法說會成長動能」顯示無官方展望，美股卻有</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>__guidanceData 只有美股路徑會設定，doSearchTW 從不設定；且它是全域變數，台股不清除會沿用上一次美股搜尋的別家公司指引。</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>台股改用官網 IR 摘要當依據；每次明確清除全域殘留。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>諾和諾德盤前股價正確，但盤前漲跌幅度錯誤</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>previousClose 並非每次都回傳，程式退回 chartPreviousClose（圖表視窗前一筆收盤），盤前取 1d 視窗會抓到前兩個交易日，基準差一天。NVO 7/31 大跌 9%，故顯示 -8.99% 而非 -0.22%。</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>基準改用 regularMarketPrice（盤前時即前一交易日收盤），與盤後同一套。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>打開 App 點產品與服務等選單顯示「建置中」，要先點 AI 鈕</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>「台股個股深度分析建置中（Phase 2 即將推出）」是 Phase 2 未完成時的過時 placeholder，台股深度分析其實早已完成，只是文字沒清掉。</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>移除過時文字＋新增自動載入。教訓：每完成一個 Phase，要一併搜尋清掉對應的 placeholder 文字。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>（我誤判）先把「沒內容」判斷成快取問題</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>使用者第一次描述症狀時我沒問完整操作路徑，直接查 Service Worker／Cache-Control／git 歷史，方向錯誤。</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>教訓：使用者說「沒內容」時，先請他描述完整操作步驟（從打開 App 到看到問題），再動手查。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>手機版公司英文長名被截斷</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>.co-info h1 用 overflow-wrap:normal，長單字（UNITED MICROELECTRONICS CORP）無法斷行，320px 下溢出容器 48px 被裁。</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>加 overflow-wrap:anywhere。教訓：驗證要加測 320px 極窄螢幕。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>（我的疏失）git add -A 誤把 Excel 鎖定暫存檔加入版控</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>用了範圍過大的 git add -A，且在同一條命令鏈中 commit，沒有機會在提交前檢查。</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>移除並把 ~$* 與 _c.js 加入 .gitignore。教訓：git add 要指定檔案，或先 status 確認再分開 commit。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>長期</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>台股深度分析曾長期顯示「建置中」而未被發現</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>我每次只驗證自己剛改的功能，沒有從「使用者打開 App 的第一步」走完整條路徑。</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>⏳ 進行中</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>改為每次交付前走完整 golden path：冷啟動→切市場→點每個選單→兩市場交叉比對。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>（我造成的回歸）編輯模式公司名被擠成一字一行直排</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>我加的 ▲▼ 按鈕多佔一欄寬度，390px 下 .wl-name 沒空間而逐字換行。加完按鈕就截圖才發現。</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>編輯模式隱藏走勢線騰出寬度＋名稱 min-width＋按鈕縮小。教訓：改動版面後一定要在 390px 截圖看實際畫面，不能只看功能通過。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>載入進度在每個選單都會冒出來</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>logPanel 夾在自選股與 results 之間，不屬於任何選單，showGroup 也沒管它。</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>移入大盤指數區塊並由 syncLogPanel() 控制。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F12"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -849,7 +2320,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1035,7 +2506,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1113,7 +2584,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/交接清單/skill架構內容.xlsx
+++ b/交接清單/skill架構內容.xlsx
@@ -15,8 +15,8 @@
     <sheet name="股票APP-台股版對照" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'需求追蹤清單'!$A$1:$F$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'錯誤紀錄'!$A$1:$F$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'需求追蹤清單'!$A$1:$F$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'錯誤紀錄'!$A$1:$F$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1527,8 +1527,274 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>版面</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>財務指標標題改為「最近10年財務指標」（台股／美股）</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>台股原「近年關鍵財務指標」、美股原「近N年財務指標」</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>一致性</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>美股與台股「關鍵財務指標」內容要一致</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>雙掛牌改用同一份 SEC 財報，10年數字逐列相同</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>一致性</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>美股有「年營收&amp;成長率」台股沒有，主旨名稱也不一致</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>台股補圖表卡並拆成三張卡，名稱與順序與美股相同</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>一致性</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>關鍵財務指標的標題名稱和順序要一致</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>兩邊皆為 公司股價區／最近10年財務指標／年營收&amp;成長率／年營收明細</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>一致性</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>台股財經新聞與美股台積電不同</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>雙掛牌改用美股代碼查新聞</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>版面</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>自選股預設改為 台積電／聯發科／鴻海／0050</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>已驗證 0050.TW 報價正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>版面</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>產品與服務移到投資總結前面</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>點財經新聞會先閃過公司股價、產品與服務才出現新聞</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>骨架渲染後立即 showGroup 收斂</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>長期</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>驗證流程</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>交付前走完整 golden path，版面改動一定截圖，跨市場並排比對</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>⏳ 進行中</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>本輪多次靠使用者回報才發現，已列為固定流程</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F34"/>
+  <autoFilter ref="A1:F43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1539,7 +1805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1912,8 +2178,188 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>台股與美股同一家台積電，財務指標數字不同</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>兩邊用不同資料源：台股 FinMind（台灣申報季度加總）、美股 SEC EDGAR。稅後淨利口徑本就差約1%（2024：1,172,200 vs 1,157,524 百萬），毛利率相同但淨利率/ROE 不同。</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>雙掛牌（TW_US_EQUIV）改用與美股相同的 SEC 財報。台積電 SEC 申報即以新台幣計價，幣別一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>台股與美股的最新新聞不同</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Yahoo 新聞查詢對 2330.TW 與 TSM 回傳不同結果。</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>雙掛牌改用美股代碼查新聞。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>（我造成的回歸）改用 SEC 後台股表格出現空白 2014 年、且少了 2025</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>只搬了 SEC 年度資料，沒比照美股「丟掉無營收年份／Yahoo 補最新年度（SEC 申報有延遲）／只留最近10年」。</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>補齊三個步驟。教訓：移植另一條管線時要連同它的後處理一起搬，不能只搬資料來源。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>（我造成的）點選單會閃過別的選單內容</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>我加的自動載入把骨架整份渲染出來，所有卡片尚未篩選，直到最後才收斂到使用者點的選單。</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>骨架渲染後立即 showGroup(__grp)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>年營收圖表為 0×0 畫不出來</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Chart.js 在 display:none 容器建立會得到 0×0（交接記錄早有記載，但只有技術分析圖做了保護）。</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>drawChart 快取 rows 並先 destroy 舊圖，showGroup(2) 發現無寬度時重畫。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>台股缺「年營收&amp;成長率」卡片、營收表塞在別的卡內</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>台股與美股的版面結構是各寫各的，沒有共用同一份卡片定義。</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>台股補上圖表卡並拆成三張卡，與美股同名同順序。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F12"/>
+  <autoFilter ref="A1:F18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/交接清單/skill架構內容.xlsx
+++ b/交接清單/skill架構內容.xlsx
@@ -15,8 +15,8 @@
     <sheet name="股票APP-台股版對照" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'需求追蹤清單'!$A$1:$F$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'錯誤紀錄'!$A$1:$F$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'需求追蹤清單'!$A$1:$F$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'錯誤紀錄'!$A$1:$F$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1793,8 +1793,368 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>一致性</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>同公司除股價/本益比外，所有選單標題與內容都要一樣</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>雙掛牌共用整份AI快取；並建立自動比對腳本，九選單已全一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>一致性</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>台股「本益比：與競爭對手相比」沒內容</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>fillCompetitorPe 原本只有美股呼叫</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>一致性</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>AI獨立分析同一天要固定，不要變來變去</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>快取鍵改為「共用代碼+當天日期」，套用到所有公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>一致性</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>台股缺投資大行目標價；美股估值卡缺目前股價</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>兩處補齊，九選單結構完全一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>版面</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>版主選股準則獨立成選單，排在投資總結前</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>新群組11</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>版面</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>大盤指數併入關鍵財務指標，指數放公司股價上面</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>指數在DOM上本就在results之前</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>版面</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>自選股移到最前面，緊接關鍵財務指標</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>預設進入頁改為自選股(避免開App就耗AI額度)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>技術分析圖的浮動數值框會擋住趨勢線</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>改為圖下方固定列顯示，tooltip external</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>搜尋後點法說會，載完卻跳到關鍵財務指標</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>新增 pickGroup()；並修正旗標設定時機</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>內容</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>台股法說會要像台積電一樣有影片，英文要有繁中即時字幕</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>新增聯發科/聯電/鴻海/日月光/國巨；改用IFrame API強制繁中字幕</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>長期</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>驗證流程</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>交付前跑雙市場一致性檢查腳本</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>⏳ 進行中</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>交接清單/雙市場一致性檢查.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>待辦</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>內容</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>其餘台股法說會影片(廣達/華碩/和碩/群聯等)</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>📅 排程中</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>需逐家搜尋並以oembed查證，每季更新</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F43"/>
+  <autoFilter ref="A1:F55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1805,7 +2165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2358,8 +2718,158 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>台積電美股與台股的AI獨立分析、競爭對手清單、法說會成長動能都不同</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>兩市場各自呼叫一次AI(本身非決定性)，且提示詞帶入各自的股價/本益比；競爭對手代碼也由AI每次重新產生。</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>整份AI結果以「共用代碼+日期」快取共用；雙掛牌提示詞改市場中立、禁止引用絕對股價與精確本益比。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>AI結論同一天內幾分鐘前後就不同</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>快取原本只套用在雙掛牌，一般公司完全沒快取。</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>快取套用到所有公司，鍵含當天日期，換日自動失效並清除舊鍵。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>（我造成的）加了 pickGroup 但選單還是被跳走</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>doSearchTW 在載入「結尾」才設 __jumpAfterSearch=true，反過來蓋掉使用者中途的手動選擇。只改一半就以為好了。</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>改在函式開頭設定。教訓：改旗標行為要追完整條時序，不能只看設定點。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>繁中字幕沒出現</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>cc_lang_pref 只是「偏好語言」，影片若無現成繁中軌不會自動翻譯。</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>改用 IFrame API 在 onReady/onPlaying 主動指定字幕軌，並試 zh-Hant/zh-TW。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>一直靠使用者一項一項回報差異（打地鼠）</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>我每次只驗證剛改的地方，沒有系統性比對兩個市場的完整結構。</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>建立 交接清單/雙市場一致性檢查.js，一次比對九個選單的卡片/小標題/欄位標籤，自動忽略合理可不同的股價與本益比。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F18"/>
+  <autoFilter ref="A1:F23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/交接清單/skill架構內容.xlsx
+++ b/交接清單/skill架構內容.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2153,6 +2153,696 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>56</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>修正</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>台股投資大行目標價漲跌幅全錯（用台幣價對比美元目標價）</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>改用 ADR 美元股價算百分比（fetchJson取美股報價）</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>57</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>修正</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>台股 Logo 顯示代碼數字（如台積電顯示"2"）而非公司名</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>co-logo 改用 o.name[0]（公司名首字）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>58</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>季度更新</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SPOT(Spotify) Q2 2026 法說會更新</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>營收47.8億歐/付費戶3億/毛利率33.4%歷史新高/Q3財測</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>59</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>一致性</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>twToUs()套用到全部4個位置:聯電/日月光/中華電統一待遇</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>SEC財報/新聞/目標價/symbolForLinks全部改用twToUs()</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>60</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>修正</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>投資大行券商報告連結打開錯誤</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>fillAnalystTargets的rptUrl被zhLink()(Google翻譯代理)包裝，代理不支援google.com自家網域必定出錯，移除包裝直接開啟</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>61</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>修正</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>法說會影片美股台積電第一次進入模糊、切第二次才清楚</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>irVideoBlock改成點擊高畫質靜態縮圖才建立iframe，不再頁面載入就用YT IFrame API接管既有iframe造成重新載入</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>62</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>投資大師選單影片間空一行空白做區隔</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>margin-bottom 14px→28px</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>63</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>投資大師影片加即時繁中字幕，不要使用者自己設定</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>重構initIrCaptions為共用函式forceZhCaptions(iframeId)，loadMasterVid播放時也自動套用</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>64</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>投資大師選單分長影片/短影音子選單，兩者數量增加</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>MASTER_VIDEOS改{long,short}結構，新增setMasterTab()切換分頁，每人新增2支Shorts(逐支核實真人畫面)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>65</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>App開啟先出現封面1.5秒，緊接直接出現自選股股價畫面</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>原本靠window.load事件計時不穩定，改用明確setTimeout(1500ms)；價格資料改立即背景抓取</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>66</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>選單改名：關鍵財務指標→大盤指數與關鍵財務指標</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>單一按鈕文字修改</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>67</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>選單改名：投資大師→投資大師學院，美股/台股都改</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>選單按鈕+美股/台股卡片標題共3處</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>68</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>投資大師學院選單移到自選股選單後面</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>調整grpMenu按鈕順序</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>69</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>財經新聞選單排在投資大師學院選單後面</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>調整grpMenu按鈕順序</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>70</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>長期/待辦</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>法說會影片和內容：美股先51間指定公司→依序S&amp;P500/道瓊/那斯達克/費半成分股；台股先0050成分股→依序上市/上櫃公司，來源皆官方網頁，法說會後自行更新不要提醒</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>📅 排程中(規模極大，需多session逐步完成)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>見交接記錄.md「使用者2026-08-06交代的長期範圍」段落；⚠️已告知使用者無背景自動更新能力，需使用者開新session請求或另設排程機制</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>71</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>季度更新</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>研華(2395) 2026上半年法說會內容更新</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>營收465.1億(+32%)、EPS 9.05元(+60%)創同期新高，來源BigGo Finance整理官方數據</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>72</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>季度更新</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NVO H1法說會內容更新(使用者發現原內容仍是舊資料)</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Q2調整後營業利益+11%CER、全年展望上修至0%~-6%CER，來源官方新聞稿+SEC 6-K</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>73</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>投資大師學院選單移到自選股選單後面</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>調整grpMenu按鈕順序</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>74</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>財經新聞選單排在投資大師學院選單後面</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>調整grpMenu按鈕順序</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>75</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>美股/台股都加入ETF到自選股公司中，讓使用者可搜尋到並加入</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>台股TW_NAMES新增5檔ETF(006208/00919/00929/0052/00713)；美股新增US_ETF清單(SPY/VOO/QQQ等16檔)+findUsEtf()備援路徑</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>76</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>自選股編輯模式新增主題概念股選單(半導體/機器人/光通訊/AI/存儲/儲能/AI PC/高股息/減肥藥)，可瀏覽相關公司股價並用愛心加入自選股</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>THEME_STOCKS資料結構(美股/台股各自成分)+setWlView()切換分頁+addThemeStockToWatchlist()</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>77</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>長期/自動化</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>法說會後自行更新，不要使用者提醒</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>✅ 已完成(排程建立)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>用RemoteTrigger建立雲端排程routine(trig_0198gQF8XQ6yS5cSSipYuNkk)，每週一晚上9點台北時間自動檢查已追蹤公司是否有新法說會/財報並更新+commit+push，不依賴本機App是否開啟</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>78</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>長期/自動化</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>排程優先順序：台股先完成0050成分股，美股先完成指定51間公司，完成後再繼續其他公司</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>更新排程prompt明訂優先順序:台股0050成分股(含新增未追蹤者)→其他上市→上櫃；美股現有IR_CALL_SUMMARY清單→S&amp;P500/道瓊/那斯達克/費半</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2165,7 +2855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2865,6 +3555,216 @@
       <c r="F23" s="6" t="inlineStr">
         <is>
           <t>建立 交接清單/雙市場一致性檢查.js，一次比對九個選單的卡片/小標題/欄位標籤，自動忽略合理可不同的股價與本益比。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>台股投資大行目標價百分比全錯(如台積電 -79%)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>fillAnalystTargets(TW_US_EQUIV[code], gen, price) 的 price 是台幣股價(NT320)，但目標價是美元(80)，(480-2320)/2320=-79%。</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>改為先 fetch ADR 美元股價再傳入。教訓：跨幣別/跨市場的比較一定要確認單位一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>投資大師選單裡巴菲特紀錄片其實只有1分鐘(使用者記得是1小時多)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>加入的jXg0V2tyhXo其實是HBO官方1分鐘預告片，標題「Becoming Warren Buffett (HBO Documentary Films)」與正片幾乎同名容易誤判，只看標題沒實際開啟確認片長</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>改用i45_qjgFmxg完整版(1小時28分)。教訓：加影片務必用瀏覽器實際打開看播放器顯示的片長，不能只信標題文字。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>投資大行券商報告連結打開必定錯誤</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>fillAnalystTargets的報告連結用zhLink()(Google翻譯代理)包裝google.com/search網址，但Google翻譯代理不支援代理Google自家網域，100%必定失敗</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>移除zhLink包裝直接開啟原始網址。教訓：加連結前想清楚目標網域是否適合套翻譯代理，不是所有外部連結都該無腦包一層zhLink。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>法說會影片美股台積電第一次進入模糊，切第二次才清楚</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>irVideoBlock頁面載入(setTimeout 0)就呼叫initIrCaptions，用new YT.Player(既有iframeId)接管既有iframe以做字幕強制切換，這個接管動作會讓iframe重新載入一次(建立postMessage橋接)，剛好被使用者看到造成模糊</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>改成點擊高畫質靜態縮圖才建立iframe+套用字幕API，不在頁面載入時自動接管。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>（自我檢查發現）待辦清單記載AAPL/MSFT/META/AMZN/GOOGL還是Q1資料</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>待辦清單本身沒有同步更新，實際內容應是先前session已完成但清單漏勾，抽查AAPL/GOOGL兩家數字與官方公布完全吻合</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>✅ 已完成(確認為清單過時非真bug)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>教訓：待辦清單可能已經過時，動手大改前先花時間抽查實際內容是否真的需要改，避免做重複無意義的工。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>（自我檢查發現）主題概念股加入自選股後，切回自選股清單看不到剛加入的股票</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>addThemeStockToWatchlist()只寫入localStorage，沒有呼叫renderWatchlist()重新產生watchlistTable的HTML，導致主題頁加入的股票要重新整理頁面才會出現在清單頁</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>加入後立即呼叫renderWatchlist()背景更新(此時可能被主題頁蓋住不可見，但切回清單頁時內容已經是新的)。教訓：任何修改getWatchlist()資料的地方，都要確認有沒有連動更新對應的DOM，不能只存localStorage就以為畫面會自己同步。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>（使用者糾正）我說「沒辦法在法說會結束後自動觸發，需要開新對話」</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>我沒有先檢查有沒有現成的排程工具就直接下結論說做不到，實際上有RemoteTrigger(雲端cron routine)可以用</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>用schedule skill建立雲端排程routine，每週自動執行檢查更新。教訓：說「做不到」之前，先確認手上工具清單有沒有相關能力，不要在沒查證前就對使用者下結論式的否定回答。</t>
         </is>
       </c>
     </row>

--- a/交接清單/skill架構內容.xlsx
+++ b/交接清單/skill架構內容.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2843,6 +2843,36 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>79</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>投資大師影片一定要有繁體中文，找其他相同影片或其他來源；新增有聲書小選單，放彼得林區選股戰略和巴菲特雪球</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>三位大師長影片第一支改用「真人畫面+燒錄繁中字幕」來源(不依賴YouTube字幕系統)；新增有聲書分頁，巴菲特傳/選股戰略/窮查理寶典各上下兩集，來源小樣兒FM頻道</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2855,7 +2885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3765,6 +3795,66 @@
       <c r="F30" t="inlineStr">
         <is>
           <t>用schedule skill建立雲端排程routine，每週自動執行檢查更新。教訓：說「做不到」之前，先確認手上工具清單有沒有相關能力，不要在沒查證前就對使用者下結論式的否定回答。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>投資大師影片一直沒有繁體中文字幕</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>深入實測YouTube IFrame API發現：自動翻譯字幕是youtube.com網頁版client端功能，setOption(captions,track,{languageCode:非原生軌})會靜默失效，法說會/演講影片多半只有單一原始語言字幕軌，無法被API強制翻譯</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>改找「真人畫面+燒錄(硬燒)中文字幕」的替代影片來源，字幕直接在畫面上不受YouTube字幕系統限制。教訓：與其死磕同一個技術方案，不如換一個從根本上不受限制的方案。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>（自我發現）commit e62a6f4 訊息貼錯，內容與訊息不符</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>複製貼上commit指令時誤用了前一個commit的舊訊息內容</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>✅ 已用git show核對確認實際diff內容正確</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>教訓：貼git commit訊息前，若前後兩次commit時間相近，要重新確認heredoc內容是這次真正要描述的變更，不能想當然爾。</t>
         </is>
       </c>
     </row>

--- a/交接清單/skill架構內容.xlsx
+++ b/交接清單/skill架構內容.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2870,6 +2870,66 @@
       <c r="F79" t="inlineStr">
         <is>
           <t>三位大師長影片第一支改用「真人畫面+燒錄繁中字幕」來源(不依賴YouTube字幕系統)；新增有聲書分頁，巴菲特傳/選股戰略/窮查理寶典各上下兩集，來源小樣兒FM頻道</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>80</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>長期/擴充</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>繼續做完0050成分股覆蓋（使用者要求"go"/"繼續做完"）</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>✅ 已完成19家(進度68%)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>新增中信金/富邦金/國泰金/兆豐金/玉山金/永豐金/華南金/台新新光金/元大金/凱基金/國巨/南亞/南亞科/光寶科/華邦電/南電/致茂/鴻勁/遠傳共19家，含法說摘要+官網業務結構，皆查證官方H1/Q2實際數字。剩16家因Q2法說會尚未召開，留給下次/排程處理</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>81</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>提醒</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>產品與服務(IR_PRODUCTS_SUMMARY)內容也要以公司官方網頁為來源</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>後續新增的業務結構介紹皆標註來源為公司官網domain</t>
         </is>
       </c>
     </row>

--- a/交接清單/skill架構內容.xlsx
+++ b/交接清單/skill架構內容.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2930,6 +2930,66 @@
       <c r="F81" t="inlineStr">
         <is>
           <t>後續新增的業務結構介紹皆標註來源為公司官網domain</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>82</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>長期/擴充</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>繼續處理美股法說會內容更新（既有已追蹤清單優先）</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>✅ 已完成13家</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>清查全部IR_CALL_SUMMARY美股條目，找出14家還停留Q1標籤(LLY/AMD/UBER/BKNG/PFE/MAR/IHG/PLTR/MCD/ANET/ABNB/AMGN/CAT/SHOP)，逐一WebSearch官方Q2 2026財報後更新13家(IHG排定8/11公布故未更新)，commit e7bf43e+236969d</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>83</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>長期/擴充</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>繼續處理台股0050成分股缺口</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>⏸️ 查證後暫緩</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>對剩餘15檔缺口(長榮/台灣大/台塑化/世芯/貿聯/健策/金像電/京元電子/奇鋐/臻鼎/第一金/合庫金/華碩/聯詠/仁寶)逐一查證，全部只有Q1實際+Q2預估或單一來源未交叉驗證的數字，依規則不寫入，建議8月中下旬後再查</t>
         </is>
       </c>
     </row>

--- a/交接清單/skill架構內容.xlsx
+++ b/交接清單/skill架構內容.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2990,6 +2990,36 @@
       <c r="F83" t="inlineStr">
         <is>
           <t>對剩餘15檔缺口(長榮/台灣大/台塑化/世芯/貿聯/健策/金像電/京元電子/奇鋐/臻鼎/第一金/合庫金/華碩/聯詠/仁寶)逐一查證，全部只有Q1實際+Q2預估或單一來源未交叉驗證的數字，依規則不寫入，建議8月中下旬後再查</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>84</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>長期/擴充</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>不用等排程，法說會內容+產品與服務美股台股都可以一次做完所有公司</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>⏳ 進行中(本次+24家)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>不中途停下來問，連續多輪WebSearch+Edit+驗證+commit：美股新增19家(PG/MRK/VZ/TXN/HON/ADBE/KLAC/NXPI/RTX/AXP/PM/TMO/ABT/DHR/LIN/UPS/BLK/MMM/CMCSA)，台股新增5家(1301/2912/6770/5347/6488)。IR_CALL_SUMMARY公司數106→130家。距離完整S&amp;P500+道瓊+那斯達克+費半、全部上市櫃台股仍有數量級落差，排程routine將接續處理長尾。</t>
         </is>
       </c>
     </row>

--- a/交接清單/skill架構內容.xlsx
+++ b/交接清單/skill架構內容.xlsx
@@ -13,6 +13,7 @@
     <sheet name="技術架構" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="已建置公司(50+)" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="股票APP-台股版對照" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="未來維護範疇(2026-08-08)" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'需求追蹤清單'!$A$1:$F$55</definedName>
@@ -25,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,8 +48,19 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -73,6 +85,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -116,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -145,6 +172,12 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -510,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3020,6 +3053,36 @@
       <c r="F84" t="inlineStr">
         <is>
           <t>不中途停下來問，連續多輪WebSearch+Edit+驗證+commit：美股新增19家(PG/MRK/VZ/TXN/HON/ADBE/KLAC/NXPI/RTX/AXP/PM/TMO/ABT/DHR/LIN/UPS/BLK/MMM/CMCSA)，台股新增5家(1301/2912/6770/5347/6488)。IR_CALL_SUMMARY公司數106→130家。距離完整S&amp;P500+道瓊+那斯達克+費半、全部上市櫃台股仍有數量級落差，排程routine將接續處理長尾。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>85</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>範疇調整</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>法說會和產品的工程太大，未來只要定期維持：1)美股台灣人最常交易100間 2)台股台灣人最常交易200間(原100，使用者當場修正為200) 3)投資主題(THEME_STOCKS)中的公司；其餘公司改用AI即時判讀，不再逐間人工建置IR常數</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>✅ 已完成(名單建立)，⏳ 台股名單待補齊</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>已在skill架構內容.xlsx新增「未來維護範疇(2026-08-08)」分頁，列出三份名單並標示已完成/未完成狀態。美股100家(81已完成)+台股200家草案(目前111檔/100已完成，尚缺89檔因0051成分股網站JS分頁無法完整擷取，待使用者提供完整清單或下次繼續查證)+投資主題美股68家(44已完成)/台股63家(46已完成)。</t>
         </is>
       </c>
     </row>
@@ -4833,4 +4896,7614 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D430"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>未來公司維護範疇說明（2026-08-08決策，2026-08-09使用者提供權威名單更新）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>法說會/產品資料人工維護（來自公司官網）範圍縮小為以下三類公司；其餘公司改用AI即時判讀，不再逐間人工建置IR常數。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1) 美股熱門交易100家(使用者提供權威名單)　2) 台股熱門交易170家(使用者提供權威名單，已移除所有ETF)　3) 投資主題(THEME_STOCKS)中引用到的公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>名單1/2為使用者2026-08-09親自提供的完整清單(取代8/8的草案版本)，已依產業分類整理，非AI推估。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>名單1：美股熱門交易100家（使用者提供）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>代碼</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>狀態</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>輝達</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>蘋果</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>微軟</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>亞馬遜</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Alphabet</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>博通</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>超微</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>英特爾</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>高通</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>美光</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>台積電ADR</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>艾司摩爾ADR</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>安謀</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>16</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>甲骨文</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>國際商業機器</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>18</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>思科</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>19</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>賽富時</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>20</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NOW</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ServiceNow</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>21</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>AMAT</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>應用材料</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>22</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>柯林研發</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>23</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>KLAC</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>科磊</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>24</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>德州儀器</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>25</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ADI</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>亞德諾半導體</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>26</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Palantir</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>27</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SNOW</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>28</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Unity</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>29</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>MDB</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MongoDB</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>30</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PATH</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>UiPath</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>31</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Cloudflare</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>32</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>33</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PANW</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Palo Alto Networks</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>34</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ZS</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Zscaler</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>35</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>DDOG</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Datadog</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>36</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>37</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>TEAM</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Atlassian</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>38</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>DOCU</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>DocuSign</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>39</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>TWLO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>40</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>OKTA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>41</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>WDAY</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>42</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>HUBS</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>HubSpot</t>
+        </is>
+      </c>
+      <c r="D49" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>43</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>MSTR</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>MicroStrategy</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>44</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>C3.ai</t>
+        </is>
+      </c>
+      <c r="D51" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>45</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>美超微</t>
+        </is>
+      </c>
+      <c r="D52" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>46</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>網飛</t>
+        </is>
+      </c>
+      <c r="D53" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>47</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Spotify</t>
+        </is>
+      </c>
+      <c r="D54" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>48</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="D55" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>49</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Booking Holdings</t>
+        </is>
+      </c>
+      <c r="D56" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>50</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="D57" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>51</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>DoorDash</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>52</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>迪士尼</t>
+        </is>
+      </c>
+      <c r="D59" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>53</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Roblox</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>54</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="D61" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>55</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SQ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>⏳ 未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>56</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="D63" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>57</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Robinhood</t>
+        </is>
+      </c>
+      <c r="D64" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>58</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Shopify</t>
+        </is>
+      </c>
+      <c r="D65" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>59</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>MELI</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>MercadoLibre</t>
+        </is>
+      </c>
+      <c r="D66" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>60</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Sea Limited(蝦皮母公司)</t>
+        </is>
+      </c>
+      <c r="D67" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>61</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ROKU</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Roku</t>
+        </is>
+      </c>
+      <c r="D68" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>62</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Snap</t>
+        </is>
+      </c>
+      <c r="D69" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>63</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Pinterest</t>
+        </is>
+      </c>
+      <c r="D70" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>64</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CHWY</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Chewy</t>
+        </is>
+      </c>
+      <c r="D71" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>65</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="D72" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>66</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>好市多</t>
+        </is>
+      </c>
+      <c r="D73" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>67</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>WMT</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>沃爾瑪</t>
+        </is>
+      </c>
+      <c r="D74" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>68</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>TGT</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>塔吉特</t>
+        </is>
+      </c>
+      <c r="D75" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>69</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SBUX</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>星巴克</t>
+        </is>
+      </c>
+      <c r="D76" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>70</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>可口可樂</t>
+        </is>
+      </c>
+      <c r="D77" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>71</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>百事可樂</t>
+        </is>
+      </c>
+      <c r="D78" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>72</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>MCD</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>麥當勞</t>
+        </is>
+      </c>
+      <c r="D79" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>73</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>NKE</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>耐吉</t>
+        </is>
+      </c>
+      <c r="D80" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>74</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>家得寶</t>
+        </is>
+      </c>
+      <c r="D81" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>75</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>勞氏</t>
+        </is>
+      </c>
+      <c r="D82" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>76</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>寶僑</t>
+        </is>
+      </c>
+      <c r="D83" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>77</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>高露潔</t>
+        </is>
+      </c>
+      <c r="D84" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>78</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>KMB</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>金百利克拉克</t>
+        </is>
+      </c>
+      <c r="D85" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>79</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>MDLZ</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>億滋國際</t>
+        </is>
+      </c>
+      <c r="D86" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>80</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>菲利普莫里斯</t>
+        </is>
+      </c>
+      <c r="D87" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>81</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>摩根大通</t>
+        </is>
+      </c>
+      <c r="D88" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>82</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>美國銀行</t>
+        </is>
+      </c>
+      <c r="D89" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>83</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>威士卡</t>
+        </is>
+      </c>
+      <c r="D90" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>84</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>萬事達卡</t>
+        </is>
+      </c>
+      <c r="D91" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>85</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>AXP</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>美國運通</t>
+        </is>
+      </c>
+      <c r="D92" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>86</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>BRK.B</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>波克夏</t>
+        </is>
+      </c>
+      <c r="D93" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>87</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>禮來</t>
+        </is>
+      </c>
+      <c r="D94" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>88</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>NVO</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>諾和諾德</t>
+        </is>
+      </c>
+      <c r="D95" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>89</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>PFE</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>輝瑞</t>
+        </is>
+      </c>
+      <c r="D96" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>90</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>JNJ</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>嬌生</t>
+        </is>
+      </c>
+      <c r="D97" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>91</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>MRK</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>默克</t>
+        </is>
+      </c>
+      <c r="D98" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>92</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ABBV</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>艾伯維</t>
+        </is>
+      </c>
+      <c r="D99" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>93</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>AMGN</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>安進</t>
+        </is>
+      </c>
+      <c r="D100" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>94</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>MRNA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>莫德納</t>
+        </is>
+      </c>
+      <c r="D101" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>95</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>GE</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>奇異</t>
+        </is>
+      </c>
+      <c r="D102" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>96</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>開拓重工</t>
+        </is>
+      </c>
+      <c r="D103" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>97</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>波音</t>
+        </is>
+      </c>
+      <c r="D104" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>98</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>LMT</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>洛克希德馬丁</t>
+        </is>
+      </c>
+      <c r="D105" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>99</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>RTX</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>雷神技術</t>
+        </is>
+      </c>
+      <c r="D106" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>100</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>漢威聯合</t>
+        </is>
+      </c>
+      <c r="D107" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="11" t="inlineStr">
+        <is>
+          <t>小計：65/100 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="109"/>
+    <row r="110">
+      <c r="A110" s="11" t="inlineStr">
+        <is>
+          <t>名單2：台股熱門交易170家（使用者提供，已移除ETF）</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="12" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t>代碼</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t>狀態</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>1</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="D112" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>2</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="D113" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>3</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>世界</t>
+        </is>
+      </c>
+      <c r="D114" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>4</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="D115" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>5</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="D116" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>6</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+      <c r="D117" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>7</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>偉詮電</t>
+        </is>
+      </c>
+      <c r="D118" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>8</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>6643</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>M31</t>
+        </is>
+      </c>
+      <c r="D119" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>9</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>3035</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>智原</t>
+        </is>
+      </c>
+      <c r="D120" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>10</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>3529</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>力旺</t>
+        </is>
+      </c>
+      <c r="D121" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>11</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>6415</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>矽力-KY</t>
+        </is>
+      </c>
+      <c r="D122" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>12</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>3034</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>聯詠</t>
+        </is>
+      </c>
+      <c r="D123" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>13</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>4961</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>天鈺</t>
+        </is>
+      </c>
+      <c r="D124" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>14</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>8016</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>矽創</t>
+        </is>
+      </c>
+      <c r="D125" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>15</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>原相</t>
+        </is>
+      </c>
+      <c r="D126" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>16</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>6531</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>愛普</t>
+        </is>
+      </c>
+      <c r="D127" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>17</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>6533</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>晶心科</t>
+        </is>
+      </c>
+      <c r="D128" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>18</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2379</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>瑞昱</t>
+        </is>
+      </c>
+      <c r="D129" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>19</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>5483</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>中美晶</t>
+        </is>
+      </c>
+      <c r="D130" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>20</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="D131" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>21</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="D132" s="14" t="inlineStr">
+        <is>
+          <t>⏳ 未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>22</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>6239</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>力成</t>
+        </is>
+      </c>
+      <c r="D133" s="14" t="inlineStr">
+        <is>
+          <t>⏳ 未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>23</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>3545</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>敦泰</t>
+        </is>
+      </c>
+      <c r="D134" s="14" t="inlineStr">
+        <is>
+          <t>⏳ 未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>24</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2458</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>義隆</t>
+        </is>
+      </c>
+      <c r="D135" s="14" t="inlineStr">
+        <is>
+          <t>⏳ 未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>25</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>8081</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>致新</t>
+        </is>
+      </c>
+      <c r="D136" s="14" t="inlineStr">
+        <is>
+          <t>⏳ 未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>26</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>3014</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>聯陽</t>
+        </is>
+      </c>
+      <c r="D137" s="14" t="inlineStr">
+        <is>
+          <t>⏳ 未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>27</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>6138</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>茂達</t>
+        </is>
+      </c>
+      <c r="D138" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>28</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>4919</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>創意/新唐</t>
+        </is>
+      </c>
+      <c r="D139" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>29</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>6756</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>威鋒電子</t>
+        </is>
+      </c>
+      <c r="D140" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>30</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>6695</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>芯鼎</t>
+        </is>
+      </c>
+      <c r="D141" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>31</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>鴻海</t>
+        </is>
+      </c>
+      <c r="D142" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>32</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+      <c r="D143" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>33</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="D144" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>34</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="D145" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>35</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>英業達</t>
+        </is>
+      </c>
+      <c r="D146" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>36</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="D147" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>37</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2324</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>仁寶</t>
+        </is>
+      </c>
+      <c r="D148" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>38</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="D149" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>39</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2376</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>技嘉</t>
+        </is>
+      </c>
+      <c r="D150" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>40</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2377</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>微星</t>
+        </is>
+      </c>
+      <c r="D151" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>41</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2352</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>佳世達</t>
+        </is>
+      </c>
+      <c r="D152" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>42</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>3005</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>神基</t>
+        </is>
+      </c>
+      <c r="D153" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>43</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2354</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>鴻準</t>
+        </is>
+      </c>
+      <c r="D154" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>44</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>3706</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>神達</t>
+        </is>
+      </c>
+      <c r="D155" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>45</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>3013</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>晟銘電</t>
+        </is>
+      </c>
+      <c r="D156" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>46</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="D157" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>47</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="D158" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>48</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="D159" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>49</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="D160" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>50</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>建準</t>
+        </is>
+      </c>
+      <c r="D161" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>51</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="D162" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>52</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>國巨</t>
+        </is>
+      </c>
+      <c r="D163" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>53</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="D164" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>54</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="D165" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>55</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="D166" s="14" t="inlineStr">
+        <is>
+          <t>⏳ 未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>56</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="D167" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>57</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>6213</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>聯茂</t>
+        </is>
+      </c>
+      <c r="D168" s="14" t="inlineStr">
+        <is>
+          <t>⏳ 未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>58</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="D169" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>59</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="D170" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>60</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>3042</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>晶技</t>
+        </is>
+      </c>
+      <c r="D171" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>61</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2492</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>華新科</t>
+        </is>
+      </c>
+      <c r="D172" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>62</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>6153</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>嘉聯益</t>
+        </is>
+      </c>
+      <c r="D173" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>63</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="D174" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>64</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>5469</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>瀚宇博</t>
+        </is>
+      </c>
+      <c r="D175" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>65</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="D176" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>66</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>6269</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>臺郡</t>
+        </is>
+      </c>
+      <c r="D177" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>67</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>立隆電</t>
+        </is>
+      </c>
+      <c r="D178" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>68</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2375</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>凱美</t>
+        </is>
+      </c>
+      <c r="D179" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>69</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2456</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>奇力新</t>
+        </is>
+      </c>
+      <c r="D180" s="14" t="inlineStr">
+        <is>
+          <t>⏳ 未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>70</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>6120</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>達運</t>
+        </is>
+      </c>
+      <c r="D181" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>71</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>3583</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>辛耘</t>
+        </is>
+      </c>
+      <c r="D182" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>72</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>3131</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>弘塑</t>
+        </is>
+      </c>
+      <c r="D183" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>73</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="D184" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>74</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>3413</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>京鼎</t>
+        </is>
+      </c>
+      <c r="D185" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>75</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>6196</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="D186" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>76</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>3680</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>家登</t>
+        </is>
+      </c>
+      <c r="D187" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>77</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="D188" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>78</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>6230</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>旭品</t>
+        </is>
+      </c>
+      <c r="D189" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>79</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>3058</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>立德</t>
+        </is>
+      </c>
+      <c r="D190" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>80</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>3376</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>新日興</t>
+        </is>
+      </c>
+      <c r="D191" s="14" t="inlineStr">
+        <is>
+          <t>⏳ 未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>81</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2465</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>麗臺</t>
+        </is>
+      </c>
+      <c r="D192" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>82</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2399</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>映泰</t>
+        </is>
+      </c>
+      <c r="D193" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>83</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>6150</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>撼訊</t>
+        </is>
+      </c>
+      <c r="D194" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>84</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2392</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>正崴</t>
+        </is>
+      </c>
+      <c r="D195" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>85</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>6271</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>同欣電</t>
+        </is>
+      </c>
+      <c r="D196" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>86</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>亞光</t>
+        </is>
+      </c>
+      <c r="D197" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>87</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>3406</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>玉晶光</t>
+        </is>
+      </c>
+      <c r="D198" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>88</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="D199" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>89</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>3362</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>先進光</t>
+        </is>
+      </c>
+      <c r="D200" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>90</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>6176</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>瑞儀</t>
+        </is>
+      </c>
+      <c r="D201" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>91</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="D202" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>92</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="D203" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>93</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2337</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="D204" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>94</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>威剛</t>
+        </is>
+      </c>
+      <c r="D205" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>95</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>8299</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>群聯</t>
+        </is>
+      </c>
+      <c r="D206" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>96</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2409</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>友達</t>
+        </is>
+      </c>
+      <c r="D207" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>97</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>群創</t>
+        </is>
+      </c>
+      <c r="D208" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>98</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>6116</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>彩晶</t>
+        </is>
+      </c>
+      <c r="D209" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>99</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2393</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>億光</t>
+        </is>
+      </c>
+      <c r="D210" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>100</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>3714</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>富采</t>
+        </is>
+      </c>
+      <c r="D211" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>101</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2406</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>國碩</t>
+        </is>
+      </c>
+      <c r="D212" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>102</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>3576</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>聯合再生</t>
+        </is>
+      </c>
+      <c r="D213" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>103</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>6244</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>茂迪</t>
+        </is>
+      </c>
+      <c r="D214" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>104</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>6443</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>元晶</t>
+        </is>
+      </c>
+      <c r="D215" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>105</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>3682</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>亞太電</t>
+        </is>
+      </c>
+      <c r="D216" s="14" t="inlineStr">
+        <is>
+          <t>⏳ 未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>106</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>3045</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>台灣大</t>
+        </is>
+      </c>
+      <c r="D217" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>107</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>4904</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>遠傳</t>
+        </is>
+      </c>
+      <c r="D218" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>108</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2412</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>中華電</t>
+        </is>
+      </c>
+      <c r="D219" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>109</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2498</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>宏達電</t>
+        </is>
+      </c>
+      <c r="D220" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>110</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2388</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>威盛</t>
+        </is>
+      </c>
+      <c r="D221" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>111</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>1513</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>中興電</t>
+        </is>
+      </c>
+      <c r="D222" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>112</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="D223" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>113</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>1504</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="D224" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>114</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>1514</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>亞力</t>
+        </is>
+      </c>
+      <c r="D225" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>115</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>1605</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="D226" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>116</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>1609</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>太電</t>
+        </is>
+      </c>
+      <c r="D227" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>117</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>6806</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>森崴能源</t>
+        </is>
+      </c>
+      <c r="D228" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>118</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>9958</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>世紀鋼</t>
+        </is>
+      </c>
+      <c r="D229" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>119</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>3708</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>上緯投控</t>
+        </is>
+      </c>
+      <c r="D230" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>120</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2634</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>漢翔</t>
+        </is>
+      </c>
+      <c r="D231" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>121</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>8222</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>寶一</t>
+        </is>
+      </c>
+      <c r="D232" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>122</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>4541</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>廣宇</t>
+        </is>
+      </c>
+      <c r="D233" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>123</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2208</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>台船</t>
+        </is>
+      </c>
+      <c r="D234" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>124</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>4572</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>美時</t>
+        </is>
+      </c>
+      <c r="D235" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>125</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>士電</t>
+        </is>
+      </c>
+      <c r="D236" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>126</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>1516</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>川飛</t>
+        </is>
+      </c>
+      <c r="D237" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>127</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>1522</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>堤維西</t>
+        </is>
+      </c>
+      <c r="D238" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>128</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>1536</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>和大</t>
+        </is>
+      </c>
+      <c r="D239" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>129</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>正新</t>
+        </is>
+      </c>
+      <c r="D240" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>130</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>裕隆</t>
+        </is>
+      </c>
+      <c r="D241" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>131</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="D242" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>132</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2882</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>國泰金</t>
+        </is>
+      </c>
+      <c r="D243" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>133</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2891</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>中信金</t>
+        </is>
+      </c>
+      <c r="D244" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>134</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2886</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>兆豐金</t>
+        </is>
+      </c>
+      <c r="D245" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>135</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="D246" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>136</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>第一金</t>
+        </is>
+      </c>
+      <c r="D247" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>137</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2880</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>華南金</t>
+        </is>
+      </c>
+      <c r="D248" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>138</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="D249" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>139</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>凱基金</t>
+        </is>
+      </c>
+      <c r="D250" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>140</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>台新金</t>
+        </is>
+      </c>
+      <c r="D251" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>141</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>永豐金</t>
+        </is>
+      </c>
+      <c r="D252" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>142</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2888</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>新光金</t>
+        </is>
+      </c>
+      <c r="D253" s="14" t="inlineStr">
+        <is>
+          <t>⏳ 未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>143</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2801</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>彰銀</t>
+        </is>
+      </c>
+      <c r="D254" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>144</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>臺企銀</t>
+        </is>
+      </c>
+      <c r="D255" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>145</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>5880</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>合庫金</t>
+        </is>
+      </c>
+      <c r="D256" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>146</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2812</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>台企銀</t>
+        </is>
+      </c>
+      <c r="D257" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>147</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2838</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>聯邦銀</t>
+        </is>
+      </c>
+      <c r="D258" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>148</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2809</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>京城銀</t>
+        </is>
+      </c>
+      <c r="D259" s="14" t="inlineStr">
+        <is>
+          <t>⏳ 未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>149</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>5871</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>中租-KY</t>
+        </is>
+      </c>
+      <c r="D260" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>150</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>5876</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>上海商銀</t>
+        </is>
+      </c>
+      <c r="D261" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>151</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2603</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>長榮</t>
+        </is>
+      </c>
+      <c r="D262" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>152</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2609</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>陽明</t>
+        </is>
+      </c>
+      <c r="D263" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>153</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2615</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>萬海</t>
+        </is>
+      </c>
+      <c r="D264" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>154</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+      <c r="D265" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>155</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2610</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>華航</t>
+        </is>
+      </c>
+      <c r="D266" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>156</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2637</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>慧洋-KY</t>
+        </is>
+      </c>
+      <c r="D267" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>157</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2606</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>裕民</t>
+        </is>
+      </c>
+      <c r="D268" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>158</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2617</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>台航</t>
+        </is>
+      </c>
+      <c r="D269" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>159</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>中鋼</t>
+        </is>
+      </c>
+      <c r="D270" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>160</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>中鴻</t>
+        </is>
+      </c>
+      <c r="D271" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>161</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>大成鋼</t>
+        </is>
+      </c>
+      <c r="D272" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>162</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>第一銅</t>
+        </is>
+      </c>
+      <c r="D273" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>163</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>台塑</t>
+        </is>
+      </c>
+      <c r="D274" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>164</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="D275" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>165</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>1326</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>台化</t>
+        </is>
+      </c>
+      <c r="D276" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>166</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>6505</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>台塑化</t>
+        </is>
+      </c>
+      <c r="D277" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>167</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="D278" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>168</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>亞泥</t>
+        </is>
+      </c>
+      <c r="D279" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>169</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>1216</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>統一</t>
+        </is>
+      </c>
+      <c r="D280" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>170</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>9904</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>寶成</t>
+        </is>
+      </c>
+      <c r="D281" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="11" t="inlineStr">
+        <is>
+          <t>小計：74/170 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="283"/>
+    <row r="284">
+      <c r="A284" s="11" t="inlineStr">
+        <is>
+          <t>名單3：投資主題(THEME_STOCKS)引用到的公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="11" t="inlineStr">
+        <is>
+          <t>美股題材成分股：</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="12" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B286" s="12" t="inlineStr">
+        <is>
+          <t>代碼</t>
+        </is>
+      </c>
+      <c r="C286" s="12" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="D286" s="12" t="inlineStr">
+        <is>
+          <t>狀態</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>1</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>AAOI</t>
+        </is>
+      </c>
+      <c r="D287" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>2</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D288" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>3</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="D289" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>4</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D290" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>5</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D291" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>6</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="D292" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>7</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="D293" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>8</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>ASTS</t>
+        </is>
+      </c>
+      <c r="D294" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>9</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D295" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>10</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>AXP</t>
+        </is>
+      </c>
+      <c r="D296" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>11</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="D297" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>12</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="D298" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>13</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="D299" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>14</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>CIEN</t>
+        </is>
+      </c>
+      <c r="D300" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>15</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>COHR</t>
+        </is>
+      </c>
+      <c r="D301" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>16</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>CVX</t>
+        </is>
+      </c>
+      <c r="D302" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>17</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="D303" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>18</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="D304" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>19</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>DLR</t>
+        </is>
+      </c>
+      <c r="D305" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>20</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>ENPH</t>
+        </is>
+      </c>
+      <c r="D306" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>21</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>EQIX</t>
+        </is>
+      </c>
+      <c r="D307" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>22</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>ETN</t>
+        </is>
+      </c>
+      <c r="D308" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>23</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>FLNC</t>
+        </is>
+      </c>
+      <c r="D309" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>24</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>FN</t>
+        </is>
+      </c>
+      <c r="D310" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>25</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D311" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>26</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="D312" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>27</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>HPE</t>
+        </is>
+      </c>
+      <c r="D313" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>28</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>HPQ</t>
+        </is>
+      </c>
+      <c r="D314" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>29</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="D315" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>30</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>IRDM</t>
+        </is>
+      </c>
+      <c r="D316" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>31</v>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>ISRG</t>
+        </is>
+      </c>
+      <c r="D317" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>32</v>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>JNJ</t>
+        </is>
+      </c>
+      <c r="D318" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>33</v>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>KHC</t>
+        </is>
+      </c>
+      <c r="D319" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>34</v>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="D320" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>35</v>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>LHX</t>
+        </is>
+      </c>
+      <c r="D321" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>36</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>LITE</t>
+        </is>
+      </c>
+      <c r="D322" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>37</v>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="D323" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>38</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>LMT</t>
+        </is>
+      </c>
+      <c r="D324" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>39</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>MCO</t>
+        </is>
+      </c>
+      <c r="D325" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>40</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D326" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>41</v>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="D327" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>42</v>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D328" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>43</v>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="D329" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>44</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>NOC</t>
+        </is>
+      </c>
+      <c r="D330" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>45</v>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>NTAP</t>
+        </is>
+      </c>
+      <c r="D331" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>46</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D332" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>47</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>NVO</t>
+        </is>
+      </c>
+      <c r="D333" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>48</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>OXY</t>
+        </is>
+      </c>
+      <c r="D334" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>49</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="D335" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>50</v>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>PFE</t>
+        </is>
+      </c>
+      <c r="D336" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>51</v>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="D337" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>52</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="D338" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>53</v>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="D339" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>54</v>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>RKLB</t>
+        </is>
+      </c>
+      <c r="D340" s="14" t="inlineStr">
+        <is>
+          <t>⏳ 未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>55</v>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>ROK</t>
+        </is>
+      </c>
+      <c r="D341" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>56</v>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>RTX</t>
+        </is>
+      </c>
+      <c r="D342" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>57</v>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>SEDG</t>
+        </is>
+      </c>
+      <c r="D343" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>58</v>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="D344" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>59</v>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>STX</t>
+        </is>
+      </c>
+      <c r="D345" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>60</v>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D346" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>61</v>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="D347" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>62</v>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="D348" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>63</v>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>VKTX</t>
+        </is>
+      </c>
+      <c r="D349" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>64</v>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>VRT</t>
+        </is>
+      </c>
+      <c r="D350" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>65</v>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="D351" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>66</v>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>VZ</t>
+        </is>
+      </c>
+      <c r="D352" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>67</v>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="D353" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>68</v>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="D354" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="11" t="inlineStr">
+        <is>
+          <t>小計：44/68 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="356"/>
+    <row r="357">
+      <c r="A357" s="11" t="inlineStr">
+        <is>
+          <t>台股題材成分股：</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="12" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B358" s="12" t="inlineStr">
+        <is>
+          <t>代碼</t>
+        </is>
+      </c>
+      <c r="C358" s="12" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="D358" s="12" t="inlineStr">
+        <is>
+          <t>狀態</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>1</v>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>1216</t>
+        </is>
+      </c>
+      <c r="D359" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>2</v>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="D360" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>3</v>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>1513</t>
+        </is>
+      </c>
+      <c r="D361" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>4</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>1514</t>
+        </is>
+      </c>
+      <c r="D362" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>5</v>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="D363" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>6</v>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>1597</t>
+        </is>
+      </c>
+      <c r="D364" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>7</v>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="D365" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>8</v>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="D366" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>9</v>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="D367" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>10</v>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="D368" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>11</v>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>2324</t>
+        </is>
+      </c>
+      <c r="D369" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>12</v>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="D370" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>13</v>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>2337</t>
+        </is>
+      </c>
+      <c r="D371" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>14</v>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="D372" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>15</v>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="D373" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>16</v>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="D374" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>17</v>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>2359</t>
+        </is>
+      </c>
+      <c r="D375" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>18</v>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>2376</t>
+        </is>
+      </c>
+      <c r="D376" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>19</v>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>2379</t>
+        </is>
+      </c>
+      <c r="D377" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>20</v>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="D378" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>21</v>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="D379" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>22</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>2412</t>
+        </is>
+      </c>
+      <c r="D380" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>23</v>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="D381" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>24</v>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>2451</t>
+        </is>
+      </c>
+      <c r="D382" s="14" t="inlineStr">
+        <is>
+          <t>⏳ 未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>25</v>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="D383" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>26</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>2634</t>
+        </is>
+      </c>
+      <c r="D384" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>27</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="D385" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>28</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>2886</t>
+        </is>
+      </c>
+      <c r="D386" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>29</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>2891</t>
+        </is>
+      </c>
+      <c r="D387" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>30</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="D388" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>31</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>3006</t>
+        </is>
+      </c>
+      <c r="D389" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>32</v>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="D390" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>33</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="D391" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>34</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>3034</t>
+        </is>
+      </c>
+      <c r="D392" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>35</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="D393" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>36</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="D394" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>37</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="D395" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>38</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>3163</t>
+        </is>
+      </c>
+      <c r="D396" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>39</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="D397" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>40</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>3234</t>
+        </is>
+      </c>
+      <c r="D398" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>41</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="D399" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>42</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="D400" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>43</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>3363</t>
+        </is>
+      </c>
+      <c r="D401" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>44</v>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>3406</t>
+        </is>
+      </c>
+      <c r="D402" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>45</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="D403" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>46</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>3450</t>
+        </is>
+      </c>
+      <c r="D404" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>47</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="D405" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>48</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="D406" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>49</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="D407" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>50</v>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="D408" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>51</v>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>4938</t>
+        </is>
+      </c>
+      <c r="D409" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>52</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>4967</t>
+        </is>
+      </c>
+      <c r="D410" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>53</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>4979</t>
+        </is>
+      </c>
+      <c r="D411" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>54</v>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>5880</t>
+        </is>
+      </c>
+      <c r="D412" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>55</v>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>6121</t>
+        </is>
+      </c>
+      <c r="D413" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>56</v>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>6442</t>
+        </is>
+      </c>
+      <c r="D414" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>57</v>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="D415" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>58</v>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="D416" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>59</v>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>6753</t>
+        </is>
+      </c>
+      <c r="D417" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>60</v>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>6770</t>
+        </is>
+      </c>
+      <c r="D418" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>61</v>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>8033</t>
+        </is>
+      </c>
+      <c r="D419" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>62</v>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>8299</t>
+        </is>
+      </c>
+      <c r="D420" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>63</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="D421" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="11" t="inlineStr">
+        <is>
+          <t>小計：46/63 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-09 更新：台股金融機構/航運鋼鐵傳產/主題股缺口本次已大量補齊</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>本次新增：臺企銀(2834)/聯邦銀(2838)/台中銀(2812)/上海商銀(5876)、慧洋-KY(2637)/裕民(2606)/台航(2617)/中鴻(2014)/大成鋼(2027)/第一銅(2009)/台泥(1101)/寶成(9904)，</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>以及投資主題(機器人/光通訊/儲能/AI PC)缺口：直得(1597)/上銀(2049)/所羅門(2359)/聯亞(3081)/波若威(3163)/光環(3234)/上詮(3363)/聯鈞(3450)/華星光(4979)/光聖(6442)/新普(6121)/十銓(4967)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>⚠️ 已下市/已合併不予新建：2888新光金(2025-07-24併入2887台新新光金，2887已有資料)、2809京城銀(2025-10-01併入2890永豐金控，2890已有資料)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>⚠️ 尚未查得資料：2009第一銅精確Q1 EPS未查得確切數字(僅有累計營收年增21.8%，已標註待補)；3450聯鈞/4979華星光/6442光聖三家官方網域本次未查得，暫以財經資訊平台頁面為來源連結。</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>⚠️⚠️ 本次因對話session的WebSearch額度(200次)用罄，尚有2筆THEME_STOCKS缺口未完成，留待下次session優先處理：創見資訊(2451，AI PC題材)、Rocket Lab(RKLB，衛星/太空題材)。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/交接清單/skill架構內容.xlsx
+++ b/交接清單/skill架構內容.xlsx
@@ -4904,7 +4904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D430"/>
+  <dimension ref="A1:D432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11256,9 +11256,9 @@
           <t>RKLB</t>
         </is>
       </c>
-      <c r="D340" s="14" t="inlineStr">
-        <is>
-          <t>⏳ 未完成</t>
+      <c r="D340" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -11863,9 +11863,9 @@
           <t>2451</t>
         </is>
       </c>
-      <c r="D382" s="14" t="inlineStr">
-        <is>
-          <t>⏳ 未完成</t>
+      <c r="D382" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -12461,6 +12461,8 @@
         </is>
       </c>
     </row>
+    <row r="423"/>
+    <row r="424"/>
     <row r="425">
       <c r="A425" s="15" t="inlineStr">
         <is>
@@ -12500,6 +12502,13 @@
       <c r="A430" t="inlineStr">
         <is>
           <t>⚠️⚠️ 本次因對話session的WebSearch額度(200次)用罄，尚有2筆THEME_STOCKS缺口未完成，留待下次session優先處理：創見資訊(2451，AI PC題材)、Rocket Lab(RKLB，衛星/太空題材)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-09 追加：創見資訊(2451)/Rocket Lab(RKLB) 已補完，THEME_STOCKS 台股/美股全數100%完成</t>
         </is>
       </c>
     </row>

--- a/交接清單/skill架構內容.xlsx
+++ b/交接清單/skill架構內容.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E237"/>
+  <dimension ref="A1:E344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4883,6 +4883,2049 @@
       <c r="A237" s="15" t="inlineStr">
         <is>
           <t>總計：198/198 可建置公司已100%完成（另2家2888/2809因下市/併購不重複建置，母公司已有資料）</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="15" t="inlineStr">
+        <is>
+          <t>名單1：美股台灣人最常交易100家（2026-08-13 補回；先前重建分頁時遺漏）</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="12" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B241" s="12" t="inlineStr">
+        <is>
+          <t>代碼</t>
+        </is>
+      </c>
+      <c r="C241" s="12" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="D241" s="12" t="inlineStr">
+        <is>
+          <t>狀態</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>1</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>蘋果</t>
+        </is>
+      </c>
+      <c r="D242" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>2</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>微軟</t>
+        </is>
+      </c>
+      <c r="D243" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>3</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>谷歌</t>
+        </is>
+      </c>
+      <c r="D244" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>4</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>亞馬遜</t>
+        </is>
+      </c>
+      <c r="D245" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>5</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D246" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>6</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>輝達</t>
+        </is>
+      </c>
+      <c r="D247" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>7</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="D248" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>8</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>博通</t>
+        </is>
+      </c>
+      <c r="D249" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>9</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>台積電ADR</t>
+        </is>
+      </c>
+      <c r="D250" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>10</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>甲骨文</t>
+        </is>
+      </c>
+      <c r="D251" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>11</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="D252" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>12</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>網飛</t>
+        </is>
+      </c>
+      <c r="D253" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>13</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>超微</t>
+        </is>
+      </c>
+      <c r="D254" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>14</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>英特爾</t>
+        </is>
+      </c>
+      <c r="D255" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>15</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>高通</t>
+        </is>
+      </c>
+      <c r="D256" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>16</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>美光</t>
+        </is>
+      </c>
+      <c r="D257" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>17</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>艾司摩爾</t>
+        </is>
+      </c>
+      <c r="D258" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>18</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>安謀</t>
+        </is>
+      </c>
+      <c r="D259" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>19</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>美超微</t>
+        </is>
+      </c>
+      <c r="D260" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>20</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>戴爾</t>
+        </is>
+      </c>
+      <c r="D261" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>21</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="D262" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>22</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>PANW</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Palo Alto Networks</t>
+        </is>
+      </c>
+      <c r="D263" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>23</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>NOW</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>ServiceNow</t>
+        </is>
+      </c>
+      <c r="D264" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>24</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Palantir</t>
+        </is>
+      </c>
+      <c r="D265" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>25</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Shopify</t>
+        </is>
+      </c>
+      <c r="D266" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>26</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="D267" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>27</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="D268" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>28</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="D269" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>29</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="D270" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>30</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>思科</t>
+        </is>
+      </c>
+      <c r="D271" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>31</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>摩根大通</t>
+        </is>
+      </c>
+      <c r="D272" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>32</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>美國銀行</t>
+        </is>
+      </c>
+      <c r="D273" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>33</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>WFC</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>富國銀行</t>
+        </is>
+      </c>
+      <c r="D274" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>34</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>高盛</t>
+        </is>
+      </c>
+      <c r="D275" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>35</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>摩根士丹利</t>
+        </is>
+      </c>
+      <c r="D276" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>36</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>威士卡</t>
+        </is>
+      </c>
+      <c r="D277" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>37</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>萬事達卡</t>
+        </is>
+      </c>
+      <c r="D278" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>38</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>AXP</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>美國運通</t>
+        </is>
+      </c>
+      <c r="D279" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>39</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>SCHW</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>嘉信理財</t>
+        </is>
+      </c>
+      <c r="D280" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>40</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>貝萊德</t>
+        </is>
+      </c>
+      <c r="D281" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>41</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>花旗</t>
+        </is>
+      </c>
+      <c r="D282" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>42</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>BRK.B</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>波克夏</t>
+        </is>
+      </c>
+      <c r="D283" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>43</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>聯合健康</t>
+        </is>
+      </c>
+      <c r="D284" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>44</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>JNJ</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>嬌生</t>
+        </is>
+      </c>
+      <c r="D285" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>45</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>禮來</t>
+        </is>
+      </c>
+      <c r="D286" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>46</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>PFE</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>輝瑞</t>
+        </is>
+      </c>
+      <c r="D287" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>47</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>ABBV</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>艾伯維</t>
+        </is>
+      </c>
+      <c r="D288" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>48</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>MRK</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>默克</t>
+        </is>
+      </c>
+      <c r="D289" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>49</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>TMO</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>賽默飛世爾</t>
+        </is>
+      </c>
+      <c r="D290" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>50</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>ABT</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>亞培</t>
+        </is>
+      </c>
+      <c r="D291" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>51</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>ISRG</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>直覺外科</t>
+        </is>
+      </c>
+      <c r="D292" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>52</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>NVO</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>諾和諾德</t>
+        </is>
+      </c>
+      <c r="D293" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>53</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>GILD</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>吉利德</t>
+        </is>
+      </c>
+      <c r="D294" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>54</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>AMGN</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>安進</t>
+        </is>
+      </c>
+      <c r="D295" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>55</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>BSX</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>波士頓科學</t>
+        </is>
+      </c>
+      <c r="D296" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>56</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>MDT</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>美敦力</t>
+        </is>
+      </c>
+      <c r="D297" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>57</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="D298" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>58</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>ELV</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Elevance Health</t>
+        </is>
+      </c>
+      <c r="D299" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>59</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>HUM</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="D300" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>60</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>BMY</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>必治妥施貴寶</t>
+        </is>
+      </c>
+      <c r="D301" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>61</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>WMT</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>沃爾瑪</t>
+        </is>
+      </c>
+      <c r="D302" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>62</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>好市多</t>
+        </is>
+      </c>
+      <c r="D303" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>63</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>家得寶</t>
+        </is>
+      </c>
+      <c r="D304" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>64</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>MCD</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>麥當勞</t>
+        </is>
+      </c>
+      <c r="D305" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>65</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>SBUX</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>星巴克</t>
+        </is>
+      </c>
+      <c r="D306" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>66</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>NKE</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>耐吉</t>
+        </is>
+      </c>
+      <c r="D307" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>67</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>迪士尼</t>
+        </is>
+      </c>
+      <c r="D308" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>68</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>可口可樂</t>
+        </is>
+      </c>
+      <c r="D309" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>69</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>百事</t>
+        </is>
+      </c>
+      <c r="D310" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>70</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>寶僑</t>
+        </is>
+      </c>
+      <c r="D311" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>71</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>菲利普莫里斯</t>
+        </is>
+      </c>
+      <c r="D312" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>72</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>CMG</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Chipotle</t>
+        </is>
+      </c>
+      <c r="D313" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>73</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>YUM</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Yum! Brands</t>
+        </is>
+      </c>
+      <c r="D314" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>74</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>埃克森美孚</t>
+        </is>
+      </c>
+      <c r="D315" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>75</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>CVX</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>雪佛龍</t>
+        </is>
+      </c>
+      <c r="D316" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>76</v>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>康菲石油</t>
+        </is>
+      </c>
+      <c r="D317" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>77</v>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D318" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>78</v>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>波音</t>
+        </is>
+      </c>
+      <c r="D319" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>79</v>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>開拓重工</t>
+        </is>
+      </c>
+      <c r="D320" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>80</v>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>GE</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>奇異</t>
+        </is>
+      </c>
+      <c r="D321" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>81</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>漢威聯合</t>
+        </is>
+      </c>
+      <c r="D322" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>82</v>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>迪爾</t>
+        </is>
+      </c>
+      <c r="D323" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>83</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>通用汽車</t>
+        </is>
+      </c>
+      <c r="D324" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>84</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>福特</t>
+        </is>
+      </c>
+      <c r="D325" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>85</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Spotify</t>
+        </is>
+      </c>
+      <c r="D326" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>86</v>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>BABA</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>阿里巴巴</t>
+        </is>
+      </c>
+      <c r="D327" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>87</v>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>PDD</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>拼多多</t>
+        </is>
+      </c>
+      <c r="D328" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>88</v>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>JD</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>京東</t>
+        </is>
+      </c>
+      <c r="D329" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>89</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>NIO</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>蔚來</t>
+        </is>
+      </c>
+      <c r="D330" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>90</v>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>XPEV</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>小鵬汽車</t>
+        </is>
+      </c>
+      <c r="D331" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>91</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>理想汽車</t>
+        </is>
+      </c>
+      <c r="D332" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>92</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="D333" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>93</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>MSTR</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>MicroStrategy</t>
+        </is>
+      </c>
+      <c r="D334" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>94</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>SOFI</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="D335" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>95</v>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>RIVN</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Rivian</t>
+        </is>
+      </c>
+      <c r="D336" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>96</v>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Robinhood</t>
+        </is>
+      </c>
+      <c r="D337" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>97</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Cloudflare</t>
+        </is>
+      </c>
+      <c r="D338" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>98</v>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>DDOG</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Datadog</t>
+        </is>
+      </c>
+      <c r="D339" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>99</v>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>ZS</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Zscaler</t>
+        </is>
+      </c>
+      <c r="D340" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>100</v>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>MELI</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>MercadoLibre</t>
+        </is>
+      </c>
+      <c r="D341" s="13" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="11" t="inlineStr">
+        <is>
+          <t>小計：100/100 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-13 稽核：美股100/100、台股198/198(另2家已下市)、投資主題135/135 — 三份白名單法說會內容全數完成。</t>
         </is>
       </c>
     </row>

--- a/交接清單/skill架構內容.xlsx
+++ b/交接清單/skill架構內容.xlsx
@@ -11287,7 +11287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -13827,6 +13827,66 @@
       <c r="F85" t="inlineStr">
         <is>
           <t>已在skill架構內容.xlsx新增「未來維護範疇(2026-08-08)」分頁，列出三份名單並標示已完成/未完成狀態。美股100家(81已完成)+台股200家草案(目前111檔/100已完成，尚缺89檔因0051成分股網站JS分頁無法完整擷取，待使用者提供完整清單或下次繼續查證)+投資主題美股68家(44已完成)/台股63家(46已完成)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>86</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>範疇/路線圖</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>三階段路線圖：第一階段(美股100+台股200+投資主題)已完成→第二階段美股S&amp;P500/道瓊/那斯達克/費半→第三階段台股全部上市公司</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>⏳ 第一階段✅完成，第二階段進行中</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>取代2026-08-09「只維持三份白名單、不再無限擴充」的決策。作業方法論不變(官網IR優先→查證→補三處常數→驗證→commit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>87</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>新功能</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ETF投資選單：8個子主題(存股試算/自選ETF/排行榜/大盤/半導體AI/高股息/主動型/槓桿)</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>⏳ 進行中</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>排行依年化報酬率；欄位:名稱代碼/股價/漲跌幅/年化報酬率/年殖利率；點列跳詳情(介紹/成分股/費用/成立年數/資產規模)；愛心加入自選ETF</t>
         </is>
       </c>
     </row>

--- a/交接清單/skill架構內容.xlsx
+++ b/交接清單/skill架構內容.xlsx
@@ -11287,7 +11287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -13881,12 +13881,72 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>⏳ 進行中</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>排行依年化報酬率；欄位:名稱代碼/股價/漲跌幅/年化報酬率/年殖利率；點列跳詳情(介紹/成分股/費用/成立年數/資產規模)；愛心加入自選ETF</t>
+          <t>8分頁完成並線上實測。100檔代碼逐檔實測存在;數字即時算(年化=adjclose CAGR、殖利率=近12月配息/現價);費用率/規模/成立日/成分股取自stockanalysis.com;台股無成分股來源改誠實說明;排行榜限成立滿3年避免新ETF年化失真;版面改兩行式解決390px擠壓</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>88</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>修正</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>盤中股價每秒即時跳動(只要價格有變化)</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>根因是api/proxy.js對所有請求統一s-maxage=300,邊緣快取擋住前端輪詢。改即時報價s-maxage=1+前端1秒輪詢+in-flight保護+變動才改DOM並閃綠紅。線上實測34秒跳11次</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>89</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>修正</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>App名稱改為美股/台股AI深度分析、第二畫面標題列字體放大</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>title/logo/封面h1/manifest.json四處更名;.header.compact logo 14→16px、市場鈕11.5→13px</t>
         </is>
       </c>
     </row>

--- a/交接清單/skill架構內容.xlsx
+++ b/交接清單/skill架構內容.xlsx
@@ -11287,7 +11287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -13947,6 +13947,66 @@
       <c r="F89" t="inlineStr">
         <is>
           <t>title/logo/封面h1/manifest.json四處更名;.header.compact logo 14→16px、市場鈕11.5→13px</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>90</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>長期/擴充</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>第二階段：美股S&amp;P500/道瓊/那斯達克/費半法說會內容與產品與服務</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>⏳ 進行中(本輪+14家)</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>先抓stockanalysis.com完整501檔S&amp;P500清單算出真實缺口(起始182/501、缺319檔)。本輪完成14家:TMUS/BX/GLW/FTNT/SO/NEM/APP/TT/PWR/KKR/INTU/WELL/CME/TJX。兩物件同為489筆、美股247家。INTU與TJX因財報尚未公布,採用最新已公布季實際數字+官方指引並於quarter欄標註,待8月下旬回頭補</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>91</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>修正</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>投資大師學院影片字幕逐支查證</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>程式化查完17支captionTracks:全部只有英文自動軌、無任何可選中文軌。《成為巴菲特》換成GyCm3gpvl5w(同紀錄片+燒錄中英字幕,已下載縮圖確認真人畫面);DNllyjjRWTc與Gu_iovmjcJs本為燒錄字幕版卻沒設noCap,導致自動翻譯字幕疊成兩層,已補上</t>
         </is>
       </c>
     </row>

--- a/交接清單/skill架構內容.xlsx
+++ b/交接清單/skill架構內容.xlsx
@@ -13971,12 +13971,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>⏳ 進行中(本輪+14家)</t>
+          <t>⏳ 進行中(本輪+20家及GOOG)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>先抓stockanalysis.com完整501檔S&amp;P500清單算出真實缺口(起始182/501、缺319檔)。本輪完成14家:TMUS/BX/GLW/FTNT/SO/NEM/APP/TT/PWR/KKR/INTU/WELL/CME/TJX。兩物件同為489筆、美股247家。INTU與TJX因財報尚未公布,採用最新已公布季實際數字+官方指引並於quarter欄標註,待8月下旬回頭補</t>
+          <t>起始美股182/501、缺319檔(清單見 交接清單/第二階段_SP500缺口清單.txt，順序即市值大到小)。本輪5批完成:TMUS/BX/GLW/FTNT/SO/NEM/APP、TT/PWR/KKR/INTU、WELL/CME/TJX、HWM/MPC/PNC/BNY、VLO/FCX，另GOOG指向GOOGL同一份物件。兩常數同為496筆、美股254家。INTU與TJX財報未公布,採最新已公布季+官方指引並標註,待8月下旬回補</t>
         </is>
       </c>
     </row>

--- a/交接清單/skill架構內容.xlsx
+++ b/交接清單/skill架構內容.xlsx
@@ -13971,12 +13971,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>⏳ 進行中(本輪+20家及GOOG)</t>
+          <t>⏳ 進行中(本輪+22家及GOOG)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>起始美股182/501、缺319檔(清單見 交接清單/第二階段_SP500缺口清單.txt，順序即市值大到小)。本輪5批完成:TMUS/BX/GLW/FTNT/SO/NEM/APP、TT/PWR/KKR/INTU、WELL/CME/TJX、HWM/MPC/PNC/BNY、VLO/FCX，另GOOG指向GOOGL同一份物件。兩常數同為496筆、美股254家。INTU與TJX財報未公布,採最新已公布季+官方指引並標註,待8月下旬回補</t>
+          <t>起始美股182/501、缺319檔(清單見 交接清單/第二階段_SP500缺口清單.txt，順序即市值大到小)。本輪6批完成:TMUS/BX/GLW/FTNT/SO/NEM/APP、TT/PWR/KKR/INTU、WELL/CME/TJX、HWM/MPC/PNC/BNY、VLO/FCX、PSX/HCA，另GOOG指向GOOGL同一份物件。兩常數同為498筆、美股256家。INTU與TJX財報未公布,採最新已公布季+官方指引並標註,待8月下旬回補 HCA為唯一財測下修者(Medicaid重審致無保險病患增加),已如實標示不美化</t>
         </is>
       </c>
     </row>

--- a/交接清單/skill架構內容.xlsx
+++ b/交接清單/skill架構內容.xlsx
@@ -11287,7 +11287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -14010,6 +14010,96 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>92</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>今日市場</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>重做「今日市場」資訊架構：使用者回報「看不懂有什麼有用的資訊、不喜歡」。改為 發生什麼→為什麼→重要嗎→接下來注意什麼</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>中文名優先(走既有ccbName)、每檔改為「今天為什麼動/對投資人代表什麼/AI判讀🟢🟡🔴」、評分降為次要、移除四個箭頭、新增市場主題與今天要注意什麼(與總結共用同一次AI呼叫零成本增加)、重大異動改底部收合</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>93</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>今日市場</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>沒有可靠資料時不可讓AI猜漲跌原因</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>無新聞一律顯示「目前沒有重大公司消息，今天股價主要受市場交易情緒影響」；AI判讀在無新聞時給中性並註明「今日無明確消息」，不拿漲跌回推情緒(循環論證)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>94</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>品質/測試</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>以真實使用者身分實測整個App並列出Bug清單後修正</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>正式站+本機共測9輪流程，找到9個問題(P0×1/P1×3/P2×4/P3×1)全部修復並回歸驗證，詳見交接記錄#73</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14022,7 +14112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -14992,6 +15082,216 @@
       <c r="F32" t="inlineStr">
         <is>
           <t>教訓：貼git commit訊息前，若前後兩次commit時間相近，要重新確認heredoc內容是這次真正要描述的變更，不能想當然爾。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>(實測發現)台股每月營收「累計YoY」顯示+869.4%，還標著資料來源為公開資訊觀測站</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>資料視窗只抓兩年，最舊幾列拿「今年8個月」比「去年只抓得到的1個月」，分母不完整</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>改為今年與去年月份數都完整才計算，否則顯示「—」。教訓：顯示錯的數字比不顯示更糟，凡是累計/比較類指標都要先確認兩邊期間對齊。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>(實測發現)台股台積電頁「AI每日更新」顯示本益比31.9/技術面18/評分30，與同頁估值卡28.2x、技術分析「強勢站穩所有均線」、今日市場60分互相矛盾</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>renderDailyStockCard 用了刻意指向美股的 __symbolForLinks(2330→TSM)，讀到ADR的評分；但每日評分是由股價推導的，兩個掛牌本來就不同</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>doSearchTW新增window.__mktCode，個股卡在台股模式改讀本市場代碼。教訓：IR官方事實可以兩市場共用，凡是「由股價推導」的東西一律不能共用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>(實測發現)2026-08-30是星期日市場休市，畫面卻寫「今日▲3.10%」「今日重大異動」</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>排程週末照跑，拿到的是上一個交易日收盤，但前端一律寫「今日」</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>產生器用Yahoo regularMarketTime+gmtoffset記錄tradeDate，前端顯示「8/28 收盤」；舊資料無此欄位時週末顯示「最近交易日」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>(實測發現)美股模式的「接下來重要事件」整排都是台泥/東元/中華電等台股法說會</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>weekEvents 產出的事件沒有依市場過濾</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>有個股代碼的事件依目前市場過濾，總體類事件(美國經濟數據/台股月營收期限)兩市場都保留。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>(實測發現)台積電頁「最新新聞」出現Cisco、Amkor、SMH基金等無關新聞</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>fillNews 沒有用 Yahoo 回傳的 relatedTickers 過濾</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>改用relatedTickers過濾，全被濾光則退回原清單避免變空白(與排程腳本fetchNews同一原則)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>(實測發現)今日市場遇到型別異常的JSON會整頁渲染中斷、API失敗殘留舊的「資料日期」、null漲跌印成「▲0.00%」</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>新程式未做型別防護；失敗分支沒清空其他區塊；null&gt;=0在JS是true</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>全部加Array.isArray防護、失敗時清空所有區塊與未讀計數、漲跌為null改顯示「—」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>(實測發現)輸入不存在的台股代碼9999顯示「台股資料載入失敗，請稍後再試」，使用者會一直重試</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>catch分支一律給通用的暫時性失敗訊息，沒有分辨「代碼不存在」</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>改為明確指出查不到該代碼並提示為4碼數字，同時保留「若代碼無誤可能是來源異常」。</t>
         </is>
       </c>
     </row>

--- a/交接清單/skill架構內容.xlsx
+++ b/交接清單/skill架構內容.xlsx
@@ -14112,7 +14112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -15292,6 +15292,96 @@
       <c r="F39" t="inlineStr">
         <is>
           <t>改為明確指出查不到該代碼並提示為4碼數字，同時保留「若代碼無誤可能是來源異常」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>(我判斷錯誤)我宣稱「重大異動誤報已於2b28a6d修好、等資料重跑就乾淨」，實際重跑後反而變20檔，19檔是「最新財報摘要已更新」</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>門檻100天太寬：台股Q2財報期間結束6/30、法定8/14前就公布，我們8/30才補建摘要，被當成公司今天發布新財報</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>改為45天(台股季報法定申報期限、美股10-Q約40~45天)。實測:100天→21檔、45天→只剩2檔真的剛公布的。教訓：資料還沒重跑前不可宣稱「已修好」，要等實際產出驗證過再說。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>(實測發現)「今天市場最重要」產出的是「設備投資」「營運展望弱化」「公司治理更正」，只是把上方個股新聞換句話說一次</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>提示詞只要求「主題名2~8字」，沒有限定必須是族群/題材層級，AI就逐檔事件各寫一則</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>提示詞改為必須是產業/族群/題材層級，且一個族群至少兩家公司有消息才算主題，寧缺勿濫、歸納不出就回空陣列。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>(實測發現)Autodesk顯示「AI判讀🔴偏負面」卻「綜合評分71/100」為全頁最高，自相矛盾</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AI判讀只反映今天的新聞面方向，綜合評分是基本面/新聞/技術/情緒/估值的加權，兩者衡量的東西不同卻並排顯示</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>評分改名為「體質評分」，頁尾加說明「AI判讀＝今天的消息方向；體質評分＝綜合體質，兩者不同向是正常的，都不是買賣建議」。</t>
         </is>
       </c>
     </row>

--- a/交接清單/skill架構內容.xlsx
+++ b/交接清單/skill架構內容.xlsx
@@ -14112,7 +14112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -15382,6 +15382,186 @@
       <c r="F42" t="inlineStr">
         <is>
           <t>評分改名為「體質評分」，頁尾加說明「AI判讀＝今天的消息方向；體質評分＝綜合體質，兩者不同向是正常的，都不是買賣建議」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>(實測發現)台股個股頁顯示英文公司名，如1213顯示「OCEANIC BEVERAGES CO INC」而非「大飲」，但自選股/今日市場顯示中文</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>doSearchTW用TW_NAMES[code]||meta.shortName，TW_NAMES只有239檔而TW_ALL有1983檔，1753檔(88.4%)會退回英文名</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>改走權威字典ccbName()。教訓：任何要顯示台股公司名的地方一律用ccbName()，永遠不要直接查TW_NAMES(交接記錄早有大立光3008同類教訓，這是同一個坑的另一處)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>(實測發現)1213顯示「目前本益比1.1x」並在版主選股準則打勾「✅本益比&lt;13」，但該公司EPS為-0.85虧損中</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Yahoo trailingPeRatio對冷門股資料很舊，1213最後一筆是2026-03-13(170天前)，卻與今天股價並列當成目前值；台積電同欄位是3天前所以熱門股沒事</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>記錄__peAsOf，超過90天標示「資料截至X」且不採計進選股準則(改判➖)。並在每次搜尋開頭清除該全域變數避免沿用上一支股票的日期。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>(實測發現)ETF 0050的版主選股準則七項全無資料，卻結論「僅通過0/7項，基本面尚未完全符合」</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>結論分支只有「通過多數」與「未通過」兩種，沒有處理「全部無資料」的情況</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>新增分支：全部無資料時說明「ETF是一籃子股票沒有自己的毛利率/ROE，此準則不適用，不等於不合格」。台股與美股兩條路徑都改。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>(實測發現)320px極窄螢幕整頁可左右晃動(scrollWidth 351&gt;320)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Chart.js的canvas在極窄寬度下超出容器，390px不會</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>加上 .chart-wrap canvas, #results canvas { max-width:100% }。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>(我的測試失誤)搜尋2330卻顯示群聯NT$2150，差點誤報成P0「顯示錯誤公司」</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>前一個逾時的javascript_tool呼叫裡的for迴圈仍在背景繼續跑，把後面的搜尋結果蓋掉</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>✅ 已釐清為非缺陷</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>單次呼叫不要超過45秒；逾時後一定要location.reload()清乾淨再繼續。已寫進測試skill。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>(我的測試失誤)把「💰年營收&amp;成長率」卡片誤判為空白卡片</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>innerText抓不到&lt;canvas&gt;內容，該卡實際是Chart.js圖表(624x500)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>✅ 已釐清為非缺陷</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>判斷卡片是否為空要同時檢查canvas/svg/img，不能只看字數。已寫進測試skill。</t>
         </is>
       </c>
     </row>

--- a/交接清單/skill架構內容.xlsx
+++ b/交接清單/skill架構內容.xlsx
@@ -11287,7 +11287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -14097,6 +14097,66 @@
       <c r="F94" t="inlineStr">
         <is>
           <t>正式站+本機共測9輪流程，找到9個問題(P0×1/P1×3/P2×4/P3×1)全部修復並回歸驗證，詳見交接記錄#73</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>95</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>法說會/建置</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>第127批人工建置(新架構data/ir/{代碼}.json)：6201/6202/6205/6206/6209</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>6206飛捷/6205詮欣取得官方簡報或財務報告原檔；6201/6202/6209查無官網法說會改用TWSE官方季報並誠實標示為上半年累計。缺口清單處理至第645行，下一批第646行(6214)開始。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>96</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>資料正確性</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>發現台股財報季別≥2其實是累計數卻被自動摘要誤標成單季(IFRS慣例：Q2財報=上半年累計)</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>⏳ 修法已寫好但stash中未提交</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>證據:台泥官方新聞稿標題「上半年獲利...每股賺0.38元」，0.38正是official.每股盈餘。下次接手git stash pop後驗證再提交，見交接記錄#77。</t>
         </is>
       </c>
     </row>
